--- a/food_beverage_order_forms/032_easter_meal_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/032_easter_meal_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'meal_a'}</t>
+          <t>meal_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Meal A'}</t>
+          <t>Meal A</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'meal_b'}</t>
+          <t>meal_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Meal B'}</t>
+          <t>Meal B</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'meal_c'}</t>
+          <t>meal_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Meal C'}</t>
+          <t>Meal C</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Spring'}</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'easter'}</t>
+          <t>easter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Easter'}</t>
+          <t>Easter</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'Summer'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'in_progress_prophets'}</t>
+          <t>in_progress_prophets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'In Progress prophets'}</t>
+          <t>In Progress prophets</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'in_progress_wizards'}</t>
+          <t>in_progress_wizards</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'In Progress wizards'}</t>
+          <t>In Progress wizards</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'in_progress_heroes'}</t>
+          <t>in_progress_heroes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'In Progress heroes'}</t>
+          <t>In Progress heroes</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_35,_'name':_20}</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 35, 'name': 20}</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_36,_'name':_30}</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 36, 'name': 30}</t>
+          <t>30</t>
         </is>
       </c>
     </row>
